--- a/Data/2024_GOA_northern_rockfish.xlsx
+++ b/Data/2024_GOA_northern_rockfish.xlsx
@@ -28226,7 +28226,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -28250,6 +28250,81 @@
           <t>Interaction</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>NGAO_fall</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GOADI_fall</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>NGAO_spring</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>GOADI_spring</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Upwelling_WGOA_spring</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Upwelling_EGOA_spring</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Wind_WGOA_spring</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>SST_WGOA_shelfedge_spring</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>SST_EGOA_shelfedge_spring</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BottomTemp_WGOA_winter</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>SST_WGOA_spring</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SST_EGOA_spring</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Neocalanus_winterspring</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Copepods_small_spring</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>post2014</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -28264,6 +28339,15 @@
       <c r="D2">
         <v>3.516817003</v>
       </c>
+      <c r="I2">
+        <v>-1.586658760087045</v>
+      </c>
+      <c r="J2">
+        <v>-1.197072107413808</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3">
@@ -28278,6 +28362,15 @@
       <c r="D3">
         <v>1.841437384</v>
       </c>
+      <c r="I3">
+        <v>-2.527488340010153</v>
+      </c>
+      <c r="J3">
+        <v>-1.671843078828776</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -28292,6 +28385,15 @@
       <c r="D4">
         <v>-2.459542378</v>
       </c>
+      <c r="I4">
+        <v>-0.3967860560666429</v>
+      </c>
+      <c r="J4">
+        <v>-0.2718773938872036</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -28306,6 +28408,21 @@
       <c r="D5">
         <v>-1.23121981</v>
       </c>
+      <c r="I5">
+        <v>0.3687909550472587</v>
+      </c>
+      <c r="J5">
+        <v>0.1785463482244327</v>
+      </c>
+      <c r="O5">
+        <v>0.1336342952559508</v>
+      </c>
+      <c r="P5">
+        <v>-0.8762296224816107</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6">
@@ -28320,6 +28437,21 @@
       <c r="D6">
         <v>0.458774236</v>
       </c>
+      <c r="I6">
+        <v>-0.9778866789603279</v>
+      </c>
+      <c r="J6">
+        <v>-1.775318803367936</v>
+      </c>
+      <c r="O6">
+        <v>0.2315416593463911</v>
+      </c>
+      <c r="P6">
+        <v>-0.4413762122837447</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -28334,6 +28466,21 @@
       <c r="D7">
         <v>-4.850575923</v>
       </c>
+      <c r="I7">
+        <v>-0.1569667513803606</v>
+      </c>
+      <c r="J7">
+        <v>-1.233592951368806</v>
+      </c>
+      <c r="O7">
+        <v>1.194123819677698</v>
+      </c>
+      <c r="P7">
+        <v>0.7537960740833871</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -28348,6 +28495,21 @@
       <c r="D8">
         <v>-0.170150852</v>
       </c>
+      <c r="I8">
+        <v>-0.2584287649014799</v>
+      </c>
+      <c r="J8">
+        <v>-0.5640441455271842</v>
+      </c>
+      <c r="O8">
+        <v>0.7112838895612394</v>
+      </c>
+      <c r="P8">
+        <v>-0.01813273050311291</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -28362,6 +28524,24 @@
       <c r="D9">
         <v>1.059713947</v>
       </c>
+      <c r="I9">
+        <v>0.07362873389491111</v>
+      </c>
+      <c r="J9">
+        <v>0.7994006954593909</v>
+      </c>
+      <c r="N9">
+        <v>-1.500845307018787</v>
+      </c>
+      <c r="O9">
+        <v>-1.053752896193805</v>
+      </c>
+      <c r="P9">
+        <v>-1.17159783535261</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -28376,6 +28556,24 @@
       <c r="D10">
         <v>-0.054470725</v>
       </c>
+      <c r="I10">
+        <v>0.4149100521023131</v>
+      </c>
+      <c r="J10">
+        <v>0.7811402734818921</v>
+      </c>
+      <c r="N10">
+        <v>-0.7227393064042266</v>
+      </c>
+      <c r="O10">
+        <v>-0.5109225247769146</v>
+      </c>
+      <c r="P10">
+        <v>-0.1503669126951538</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -28390,6 +28588,24 @@
       <c r="D11">
         <v>1.113190057</v>
       </c>
+      <c r="I11">
+        <v>1.02368213322903</v>
+      </c>
+      <c r="J11">
+        <v>0.7872270808077251</v>
+      </c>
+      <c r="N11">
+        <v>-1.299797156711016</v>
+      </c>
+      <c r="O11">
+        <v>-0.8872756569414674</v>
+      </c>
+      <c r="P11">
+        <v>-1.179692957644779</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
@@ -28404,6 +28620,24 @@
       <c r="D12">
         <v>-1.088323744</v>
       </c>
+      <c r="I12">
+        <v>0.03673345625086776</v>
+      </c>
+      <c r="J12">
+        <v>-0.4057871550555281</v>
+      </c>
+      <c r="N12">
+        <v>0.1220316129381622</v>
+      </c>
+      <c r="O12">
+        <v>0.3562790365278825</v>
+      </c>
+      <c r="P12">
+        <v>0.4685410012735811</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -28418,6 +28652,36 @@
       <c r="D13">
         <v>0.282455789</v>
       </c>
+      <c r="E13">
+        <v>1.445269918880395</v>
+      </c>
+      <c r="F13">
+        <v>1.544499714666264</v>
+      </c>
+      <c r="G13">
+        <v>0.3251304867620833</v>
+      </c>
+      <c r="H13">
+        <v>-0.2969642740884098</v>
+      </c>
+      <c r="I13">
+        <v>1.005234494407009</v>
+      </c>
+      <c r="J13">
+        <v>0.5802756317294055</v>
+      </c>
+      <c r="N13">
+        <v>-0.1240228863801579</v>
+      </c>
+      <c r="O13">
+        <v>-0.1488041495666886</v>
+      </c>
+      <c r="P13">
+        <v>-0.08685133181900982</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -28432,6 +28696,36 @@
       <c r="D14">
         <v>0.5622952</v>
       </c>
+      <c r="E14">
+        <v>-0.4938731039064623</v>
+      </c>
+      <c r="F14">
+        <v>0.7873268064860137</v>
+      </c>
+      <c r="G14">
+        <v>0.942623281894989</v>
+      </c>
+      <c r="H14">
+        <v>0.8072372651204692</v>
+      </c>
+      <c r="I14">
+        <v>0.1566431085940091</v>
+      </c>
+      <c r="J14">
+        <v>-0.7466483653021719</v>
+      </c>
+      <c r="N14">
+        <v>-0.1824584863686786</v>
+      </c>
+      <c r="O14">
+        <v>-0.1541855826390538</v>
+      </c>
+      <c r="P14">
+        <v>-0.2518673027203334</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15">
@@ -28446,6 +28740,36 @@
       <c r="D15">
         <v>-0.527635564</v>
       </c>
+      <c r="E15">
+        <v>-0.2626149574125437</v>
+      </c>
+      <c r="F15">
+        <v>-0.1459002670012289</v>
+      </c>
+      <c r="G15">
+        <v>0.3744578853354592</v>
+      </c>
+      <c r="H15">
+        <v>-0.1424280880049417</v>
+      </c>
+      <c r="I15">
+        <v>-0.2123096678464255</v>
+      </c>
+      <c r="J15">
+        <v>-0.05883913748305128</v>
+      </c>
+      <c r="N15">
+        <v>-1.401274120475838</v>
+      </c>
+      <c r="O15">
+        <v>-0.6289668648329748</v>
+      </c>
+      <c r="P15">
+        <v>-0.6267337766556293</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -28460,6 +28784,36 @@
       <c r="D16">
         <v>3.80644156</v>
       </c>
+      <c r="E16">
+        <v>-0.4811127001910883</v>
+      </c>
+      <c r="F16">
+        <v>0.2736000427599957</v>
+      </c>
+      <c r="G16">
+        <v>0.1426732590406109</v>
+      </c>
+      <c r="H16">
+        <v>0.2317037833756161</v>
+      </c>
+      <c r="I16">
+        <v>0.5901626209115197</v>
+      </c>
+      <c r="J16">
+        <v>0.1907199628760982</v>
+      </c>
+      <c r="N16">
+        <v>-0.3937177467285613</v>
+      </c>
+      <c r="O16">
+        <v>0.08144210890859221</v>
+      </c>
+      <c r="P16">
+        <v>-0.4378913886267728</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17">
@@ -28474,6 +28828,39 @@
       <c r="D17">
         <v>0.112989308</v>
       </c>
+      <c r="E17">
+        <v>0.2392512207146428</v>
+      </c>
+      <c r="F17">
+        <v>-2.024308152036625</v>
+      </c>
+      <c r="G17">
+        <v>-0.2377829196959479</v>
+      </c>
+      <c r="H17">
+        <v>-0.3707315994180297</v>
+      </c>
+      <c r="I17">
+        <v>-0.1938620290244039</v>
+      </c>
+      <c r="J17">
+        <v>-0.1501412473705451</v>
+      </c>
+      <c r="N17">
+        <v>-0.09353830032496796</v>
+      </c>
+      <c r="O17">
+        <v>-0.6879890348610053</v>
+      </c>
+      <c r="P17">
+        <v>-0.8488307453259482</v>
+      </c>
+      <c r="Q17">
+        <v>-0.9765882267216606</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -28488,6 +28875,42 @@
       <c r="D18">
         <v>5.007833008</v>
       </c>
+      <c r="E18">
+        <v>-0.6277284584860268</v>
+      </c>
+      <c r="F18">
+        <v>0.1681050800828977</v>
+      </c>
+      <c r="G18">
+        <v>0.2699574650153835</v>
+      </c>
+      <c r="H18">
+        <v>-1.228834694065127</v>
+      </c>
+      <c r="I18">
+        <v>-0.8210817489731429</v>
+      </c>
+      <c r="J18">
+        <v>-2.414433572580393</v>
+      </c>
+      <c r="N18">
+        <v>1.594964490706552</v>
+      </c>
+      <c r="O18">
+        <v>1.241862339167063</v>
+      </c>
+      <c r="P18">
+        <v>2.146572394153448</v>
+      </c>
+      <c r="Q18">
+        <v>-0.845396303453731</v>
+      </c>
+      <c r="R18">
+        <v>0.08565677506139367</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -28502,6 +28925,39 @@
       <c r="D19">
         <v>24.56948677</v>
       </c>
+      <c r="E19">
+        <v>-1.586908519875893</v>
+      </c>
+      <c r="F19">
+        <v>0.009142523698577086</v>
+      </c>
+      <c r="G19">
+        <v>-1.083018908177757</v>
+      </c>
+      <c r="H19">
+        <v>0.4497186040499443</v>
+      </c>
+      <c r="I19">
+        <v>-0.5812624442868602</v>
+      </c>
+      <c r="J19">
+        <v>-0.2231829352805404</v>
+      </c>
+      <c r="O19">
+        <v>-1.554399776506671</v>
+      </c>
+      <c r="P19">
+        <v>-0.2174111381848717</v>
+      </c>
+      <c r="Q19">
+        <v>-1.188651883510917</v>
+      </c>
+      <c r="R19">
+        <v>-0.0539282891510787</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -28516,6 +28972,42 @@
       <c r="D20">
         <v>5.641400293</v>
       </c>
+      <c r="E20">
+        <v>-0.8961784940933015</v>
+      </c>
+      <c r="F20">
+        <v>-0.01518399212475957</v>
+      </c>
+      <c r="G20">
+        <v>-1.58238626511126</v>
+      </c>
+      <c r="H20">
+        <v>-0.1430373629733336</v>
+      </c>
+      <c r="I20">
+        <v>0.8668772032418457</v>
+      </c>
+      <c r="J20">
+        <v>-0.503176072268855</v>
+      </c>
+      <c r="N20">
+        <v>0.3173724835659788</v>
+      </c>
+      <c r="O20">
+        <v>-0.4253153017011546</v>
+      </c>
+      <c r="P20">
+        <v>-0.0160801211311893</v>
+      </c>
+      <c r="Q20">
+        <v>2.185197029023237</v>
+      </c>
+      <c r="R20">
+        <v>2.628294513363096</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21">
@@ -28530,6 +29022,42 @@
       <c r="D21">
         <v>0.403481291</v>
       </c>
+      <c r="E21">
+        <v>-1.5260362265812</v>
+      </c>
+      <c r="F21">
+        <v>-0.4834835729560928</v>
+      </c>
+      <c r="G21">
+        <v>-0.7324783841122158</v>
+      </c>
+      <c r="H21">
+        <v>0.3904160238563756</v>
+      </c>
+      <c r="I21">
+        <v>0.9867868555849869</v>
+      </c>
+      <c r="J21">
+        <v>-1.288374217301302</v>
+      </c>
+      <c r="N21">
+        <v>1.183751170839948</v>
+      </c>
+      <c r="O21">
+        <v>0.8422475277632582</v>
+      </c>
+      <c r="P21">
+        <v>0.2682962510710251</v>
+      </c>
+      <c r="Q21">
+        <v>-0.8759478472284544</v>
+      </c>
+      <c r="R21">
+        <v>-0.3522571518796961</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -28544,6 +29072,42 @@
       <c r="D22">
         <v>-1.18757852</v>
       </c>
+      <c r="E22">
+        <v>0.3229937476645285</v>
+      </c>
+      <c r="F22">
+        <v>-1.194489956072275</v>
+      </c>
+      <c r="G22">
+        <v>-1.151299898701534</v>
+      </c>
+      <c r="H22">
+        <v>0.3456520824750177</v>
+      </c>
+      <c r="I22">
+        <v>1.328068173792389</v>
+      </c>
+      <c r="J22">
+        <v>0.8541819613918871</v>
+      </c>
+      <c r="N22">
+        <v>-0.3092366082883931</v>
+      </c>
+      <c r="O22">
+        <v>-0.6036220511079652</v>
+      </c>
+      <c r="P22">
+        <v>-1.077984999528716</v>
+      </c>
+      <c r="Q22">
+        <v>-1.413475302700204</v>
+      </c>
+      <c r="R22">
+        <v>1.090121844982518</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -28558,6 +29122,42 @@
       <c r="D23">
         <v>-1.860474396</v>
       </c>
+      <c r="E23">
+        <v>0.8024170161508102</v>
+      </c>
+      <c r="F23">
+        <v>-0.9923161003011506</v>
+      </c>
+      <c r="G23">
+        <v>1.073295069237115</v>
+      </c>
+      <c r="H23">
+        <v>-0.5363074619117034</v>
+      </c>
+      <c r="I23">
+        <v>0.4425815103353458</v>
+      </c>
+      <c r="J23">
+        <v>-0.07709955946055032</v>
+      </c>
+      <c r="N23">
+        <v>1.582423722214906</v>
+      </c>
+      <c r="O23">
+        <v>1.899959539537328</v>
+      </c>
+      <c r="P23">
+        <v>1.493565790538557</v>
+      </c>
+      <c r="Q23">
+        <v>-0.546470414363791</v>
+      </c>
+      <c r="R23">
+        <v>-0.2592004424047145</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24">
@@ -28572,6 +29172,45 @@
       <c r="D24">
         <v>1.359503968</v>
       </c>
+      <c r="E24">
+        <v>1.502890606886395</v>
+      </c>
+      <c r="F24">
+        <v>1.557748488901428</v>
+      </c>
+      <c r="G24">
+        <v>1.216573108618108</v>
+      </c>
+      <c r="H24">
+        <v>-0.7134179873730475</v>
+      </c>
+      <c r="I24">
+        <v>-0.4705766113547299</v>
+      </c>
+      <c r="J24">
+        <v>0.3368033386960887</v>
+      </c>
+      <c r="K24">
+        <v>0.8176440453809124</v>
+      </c>
+      <c r="N24">
+        <v>0.1829698375547877</v>
+      </c>
+      <c r="O24">
+        <v>0.003677505234215223</v>
+      </c>
+      <c r="P24">
+        <v>0.3523632989996894</v>
+      </c>
+      <c r="Q24">
+        <v>-0.6842518862890138</v>
+      </c>
+      <c r="R24">
+        <v>1.402135517928045</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -28586,6 +29225,51 @@
       <c r="D25">
         <v>-0.456588483</v>
       </c>
+      <c r="E25">
+        <v>1.22358780541364</v>
+      </c>
+      <c r="F25">
+        <v>0.269691365951943</v>
+      </c>
+      <c r="G25">
+        <v>1.847950184184305</v>
+      </c>
+      <c r="H25">
+        <v>0.9078563775639757</v>
+      </c>
+      <c r="I25">
+        <v>-0.3229955007785562</v>
+      </c>
+      <c r="J25">
+        <v>0.7994006954593909</v>
+      </c>
+      <c r="K25">
+        <v>-0.6054775860927571</v>
+      </c>
+      <c r="L25">
+        <v>1.20035315347517</v>
+      </c>
+      <c r="M25">
+        <v>0.9773369103089787</v>
+      </c>
+      <c r="N25">
+        <v>0.5363564680718711</v>
+      </c>
+      <c r="O25">
+        <v>0.3355248362161071</v>
+      </c>
+      <c r="P25">
+        <v>0.2712021932592974</v>
+      </c>
+      <c r="Q25">
+        <v>0.08852245624810572</v>
+      </c>
+      <c r="R25">
+        <v>0.8629539953818278</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -28600,6 +29284,51 @@
       <c r="D26">
         <v>1.455477549</v>
       </c>
+      <c r="E26">
+        <v>0.2396335856655696</v>
+      </c>
+      <c r="F26">
+        <v>0.4491563137397152</v>
+      </c>
+      <c r="G26">
+        <v>0.695387766095707</v>
+      </c>
+      <c r="H26">
+        <v>-0.1979641244514773</v>
+      </c>
+      <c r="I26">
+        <v>-0.5535909860538278</v>
+      </c>
+      <c r="J26">
+        <v>0.4463658705610812</v>
+      </c>
+      <c r="K26">
+        <v>-0.1345361499760979</v>
+      </c>
+      <c r="L26">
+        <v>-0.8548263452062692</v>
+      </c>
+      <c r="M26">
+        <v>-0.5477147167806249</v>
+      </c>
+      <c r="N26">
+        <v>-0.3130099724113823</v>
+      </c>
+      <c r="O26">
+        <v>-0.3211836062853265</v>
+      </c>
+      <c r="P26">
+        <v>0.03499065167673084</v>
+      </c>
+      <c r="Q26">
+        <v>-0.7920808643174491</v>
+      </c>
+      <c r="R26">
+        <v>1.801731976261789</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
@@ -28614,6 +29343,48 @@
       <c r="D27">
         <v>-7.544275203</v>
       </c>
+      <c r="E27">
+        <v>-0.6147057422903903</v>
+      </c>
+      <c r="F27">
+        <v>0.9792155170437181</v>
+      </c>
+      <c r="G27">
+        <v>-0.4204075167825477</v>
+      </c>
+      <c r="H27">
+        <v>0.9439869023083833</v>
+      </c>
+      <c r="I27">
+        <v>-1.835701884184338</v>
+      </c>
+      <c r="J27">
+        <v>-0.5153496869205206</v>
+      </c>
+      <c r="L27">
+        <v>-0.4963623189602213</v>
+      </c>
+      <c r="M27">
+        <v>-0.8390548926951407</v>
+      </c>
+      <c r="N27">
+        <v>-1.731583389344625</v>
+      </c>
+      <c r="O27">
+        <v>-1.736847721208119</v>
+      </c>
+      <c r="P27">
+        <v>-1.224112351748312</v>
+      </c>
+      <c r="Q27">
+        <v>0.8133728085503652</v>
+      </c>
+      <c r="R27">
+        <v>-0.2345677840142783</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -28628,6 +29399,48 @@
       <c r="D28">
         <v>-0.812621889</v>
       </c>
+      <c r="E28">
+        <v>-1.41479673447299</v>
+      </c>
+      <c r="F28">
+        <v>0.4485989414247834</v>
+      </c>
+      <c r="G28">
+        <v>-1.00094886746584</v>
+      </c>
+      <c r="H28">
+        <v>0.4400235127841803</v>
+      </c>
+      <c r="I28">
+        <v>-1.374510913633795</v>
+      </c>
+      <c r="J28">
+        <v>-0.2292697426063734</v>
+      </c>
+      <c r="L28">
+        <v>-1.203098723069185</v>
+      </c>
+      <c r="M28">
+        <v>-2.233753975578356</v>
+      </c>
+      <c r="N28">
+        <v>-0.1795447556075346</v>
+      </c>
+      <c r="O28">
+        <v>-1.224419553034377</v>
+      </c>
+      <c r="P28">
+        <v>-1.234509165121465</v>
+      </c>
+      <c r="Q28">
+        <v>1.190774231649889</v>
+      </c>
+      <c r="R28">
+        <v>-0.4589986715715867</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -28642,6 +29455,51 @@
       <c r="D29">
         <v>2.173252863</v>
       </c>
+      <c r="E29">
+        <v>-0.6299135200197661</v>
+      </c>
+      <c r="F29">
+        <v>-0.4751098365557246</v>
+      </c>
+      <c r="G29">
+        <v>-1.345547821676793</v>
+      </c>
+      <c r="H29">
+        <v>1.528401076594845</v>
+      </c>
+      <c r="I29">
+        <v>0.1289716503609764</v>
+      </c>
+      <c r="J29">
+        <v>0.5376679804485751</v>
+      </c>
+      <c r="K29">
+        <v>-0.3439735504901</v>
+      </c>
+      <c r="L29">
+        <v>-1.157771721487676</v>
+      </c>
+      <c r="M29">
+        <v>-0.5959500010801777</v>
+      </c>
+      <c r="N29">
+        <v>-1.381604413841426</v>
+      </c>
+      <c r="O29">
+        <v>-1.599187188035382</v>
+      </c>
+      <c r="P29">
+        <v>-1.827925513642841</v>
+      </c>
+      <c r="Q29">
+        <v>-0.3427934558656353</v>
+      </c>
+      <c r="R29">
+        <v>-0.4562617095282048</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -28656,6 +29514,51 @@
       <c r="D30">
         <v>-5.35632399</v>
       </c>
+      <c r="E30">
+        <v>-0.3883939789720992</v>
+      </c>
+      <c r="F30">
+        <v>-0.688356482723427</v>
+      </c>
+      <c r="G30">
+        <v>-0.2795220489400009</v>
+      </c>
+      <c r="H30">
+        <v>-1.965366997512885</v>
+      </c>
+      <c r="I30">
+        <v>-0.000161821393175896</v>
+      </c>
+      <c r="J30">
+        <v>-1.312721446604634</v>
+      </c>
+      <c r="K30">
+        <v>-0.07983016498073886</v>
+      </c>
+      <c r="L30">
+        <v>-1.23076085067849</v>
+      </c>
+      <c r="M30">
+        <v>-1.054093231194403</v>
+      </c>
+      <c r="N30">
+        <v>0.1249729508016714</v>
+      </c>
+      <c r="O30">
+        <v>0.19300365436494</v>
+      </c>
+      <c r="P30">
+        <v>0.7585701217002138</v>
+      </c>
+      <c r="Q30">
+        <v>1.094926251180169</v>
+      </c>
+      <c r="R30">
+        <v>0.4387248786576471</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -28670,6 +29573,48 @@
       <c r="D31">
         <v>-0.314341115</v>
       </c>
+      <c r="E31">
+        <v>-0.6104024837349024</v>
+      </c>
+      <c r="F31">
+        <v>1.23395954240547</v>
+      </c>
+      <c r="G31">
+        <v>-0.5682467040694603</v>
+      </c>
+      <c r="H31">
+        <v>0.07534945105974071</v>
+      </c>
+      <c r="I31">
+        <v>1.143591785572172</v>
+      </c>
+      <c r="J31">
+        <v>1.639380106424335</v>
+      </c>
+      <c r="K31">
+        <v>0.5427589058292632</v>
+      </c>
+      <c r="L31">
+        <v>-0.6467043618488929</v>
+      </c>
+      <c r="M31">
+        <v>-0.1494508640549699</v>
+      </c>
+      <c r="O31">
+        <v>-0.4663087070161878</v>
+      </c>
+      <c r="P31">
+        <v>-0.9013452617216497</v>
+      </c>
+      <c r="Q31">
+        <v>0.495876373244417</v>
+      </c>
+      <c r="R31">
+        <v>-1.080289055419258</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -28684,6 +29629,51 @@
       <c r="D32">
         <v>-0.964351532</v>
       </c>
+      <c r="E32">
+        <v>-0.6270648809031144</v>
+      </c>
+      <c r="F32">
+        <v>-0.07575987408658073</v>
+      </c>
+      <c r="G32">
+        <v>-0.963570589106337</v>
+      </c>
+      <c r="H32">
+        <v>0.250957501656326</v>
+      </c>
+      <c r="I32">
+        <v>1.226606160271269</v>
+      </c>
+      <c r="J32">
+        <v>0.5011471364935774</v>
+      </c>
+      <c r="K32">
+        <v>-0.6984777921058796</v>
+      </c>
+      <c r="L32">
+        <v>-1.063169302221645</v>
+      </c>
+      <c r="M32">
+        <v>-1.738487877566256</v>
+      </c>
+      <c r="N32">
+        <v>-2.00698429372566</v>
+      </c>
+      <c r="O32">
+        <v>-1.99056397175323</v>
+      </c>
+      <c r="P32">
+        <v>-0.6944675859800674</v>
+      </c>
+      <c r="Q32">
+        <v>1.005068769489806</v>
+      </c>
+      <c r="R32">
+        <v>-0.2619374044480964</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
@@ -28698,6 +29688,51 @@
       <c r="D33">
         <v>-4.869979288</v>
       </c>
+      <c r="E33">
+        <v>-0.0002980996274519569</v>
+      </c>
+      <c r="F33">
+        <v>1.56078440083869</v>
+      </c>
+      <c r="G33">
+        <v>-0.6421317041586061</v>
+      </c>
+      <c r="H33">
+        <v>1.361814865544051</v>
+      </c>
+      <c r="I33">
+        <v>1.392634909669465</v>
+      </c>
+      <c r="J33">
+        <v>1.018525759189376</v>
+      </c>
+      <c r="K33">
+        <v>-2.394716723149608</v>
+      </c>
+      <c r="L33">
+        <v>-0.4321789020344631</v>
+      </c>
+      <c r="M33">
+        <v>0.8193049949423478</v>
+      </c>
+      <c r="N33">
+        <v>0.03114962480670557</v>
+      </c>
+      <c r="O33">
+        <v>-0.6381673793408894</v>
+      </c>
+      <c r="P33">
+        <v>-0.479153453341897</v>
+      </c>
+      <c r="Q33">
+        <v>0.3161614098636916</v>
+      </c>
+      <c r="R33">
+        <v>0.602942601260556</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -28712,6 +29747,51 @@
       <c r="D34">
         <v>3.538468064</v>
       </c>
+      <c r="E34">
+        <v>1.526418832240674</v>
+      </c>
+      <c r="F34">
+        <v>-2.031083705591194</v>
+      </c>
+      <c r="G34">
+        <v>0.7904491322108514</v>
+      </c>
+      <c r="H34">
+        <v>0.5176013172139986</v>
+      </c>
+      <c r="I34">
+        <v>0.9498915779409434</v>
+      </c>
+      <c r="J34">
+        <v>0.9820049152343786</v>
+      </c>
+      <c r="K34">
+        <v>1.140910124778422</v>
+      </c>
+      <c r="L34">
+        <v>0.6793955015730749</v>
+      </c>
+      <c r="M34">
+        <v>0.4867563873849935</v>
+      </c>
+      <c r="N34">
+        <v>0.2538361208018339</v>
+      </c>
+      <c r="O34">
+        <v>0.1162748334830006</v>
+      </c>
+      <c r="P34">
+        <v>-0.3581417403623396</v>
+      </c>
+      <c r="Q34">
+        <v>0.2862089159669038</v>
+      </c>
+      <c r="R34">
+        <v>0.1157633575385937</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35">
@@ -28726,6 +29806,51 @@
       <c r="D35">
         <v>-1.23197942</v>
       </c>
+      <c r="E35">
+        <v>1.527019605137757</v>
+      </c>
+      <c r="F35">
+        <v>-0.3302468726901204</v>
+      </c>
+      <c r="G35">
+        <v>2.322536687168062</v>
+      </c>
+      <c r="H35">
+        <v>-1.021075685379735</v>
+      </c>
+      <c r="I35">
+        <v>0.5901626209115197</v>
+      </c>
+      <c r="J35">
+        <v>0.4585394852127472</v>
+      </c>
+      <c r="K35">
+        <v>2.131254103024109</v>
+      </c>
+      <c r="L35">
+        <v>1.002394250336535</v>
+      </c>
+      <c r="M35">
+        <v>1.131445104847721</v>
+      </c>
+      <c r="N35">
+        <v>1.106887520845018</v>
+      </c>
+      <c r="O35">
+        <v>1.65814223572689</v>
+      </c>
+      <c r="P35">
+        <v>1.984047227411281</v>
+      </c>
+      <c r="Q35">
+        <v>-0.04925901567711715</v>
+      </c>
+      <c r="R35">
+        <v>-0.4644725956583503</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -28740,6 +29865,51 @@
       <c r="D36">
         <v>-8.131031760999999</v>
       </c>
+      <c r="E36">
+        <v>0.7113871179611621</v>
+      </c>
+      <c r="F36">
+        <v>-1.728674745081147</v>
+      </c>
+      <c r="G36">
+        <v>1.26083516710804</v>
+      </c>
+      <c r="H36">
+        <v>-2.513617827254016</v>
+      </c>
+      <c r="I36">
+        <v>-0.7380673742740452</v>
+      </c>
+      <c r="J36">
+        <v>-1.227506144042973</v>
+      </c>
+      <c r="K36">
+        <v>0.8395602687190553</v>
+      </c>
+      <c r="L36">
+        <v>1.829666999221574</v>
+      </c>
+      <c r="M36">
+        <v>1.25217886290261</v>
+      </c>
+      <c r="N36">
+        <v>2.014258273652448</v>
+      </c>
+      <c r="O36">
+        <v>2.224689490497064</v>
+      </c>
+      <c r="P36">
+        <v>2.608181224119936</v>
+      </c>
+      <c r="Q36">
+        <v>0.7235153268600025</v>
+      </c>
+      <c r="R36">
+        <v>1.421294252231717</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -28754,6 +29924,51 @@
       <c r="D37">
         <v>0.034068349</v>
       </c>
+      <c r="E37">
+        <v>0.1145738667602701</v>
+      </c>
+      <c r="F37">
+        <v>0.2990128769102303</v>
+      </c>
+      <c r="G37">
+        <v>-0.178918935871052</v>
+      </c>
+      <c r="H37">
+        <v>-0.5349967232615523</v>
+      </c>
+      <c r="I37">
+        <v>0.1197478309499654</v>
+      </c>
+      <c r="J37">
+        <v>1.243737630245194</v>
+      </c>
+      <c r="K37">
+        <v>0.06806394756400165</v>
+      </c>
+      <c r="L37">
+        <v>0.4920220563078987</v>
+      </c>
+      <c r="M37">
+        <v>0.3387623369791818</v>
+      </c>
+      <c r="N37">
+        <v>-0.4013006136745041</v>
+      </c>
+      <c r="O37">
+        <v>0.5065155350659137</v>
+      </c>
+      <c r="P37">
+        <v>0.7961397965148312</v>
+      </c>
+      <c r="Q37">
+        <v>-0.384726947321138</v>
+      </c>
+      <c r="R37">
+        <v>0.1513438641025571</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -28768,6 +29983,48 @@
       <c r="D38">
         <v>-0.9485435129999999</v>
       </c>
+      <c r="E38">
+        <v>0.9234437993902195</v>
+      </c>
+      <c r="F38">
+        <v>-0.5552213172277176</v>
+      </c>
+      <c r="G38">
+        <v>-0.04878063884053472</v>
+      </c>
+      <c r="H38">
+        <v>0.4497779361193259</v>
+      </c>
+      <c r="I38">
+        <v>0.6731769956106174</v>
+      </c>
+      <c r="J38">
+        <v>0.8115743101110566</v>
+      </c>
+      <c r="L38">
+        <v>-0.4539807336627129</v>
+      </c>
+      <c r="M38">
+        <v>0.4084599054535835</v>
+      </c>
+      <c r="N38">
+        <v>0.2804770585192993</v>
+      </c>
+      <c r="O38">
+        <v>0.7070173197022309</v>
+      </c>
+      <c r="P38">
+        <v>0.22989630943492</v>
+      </c>
+      <c r="Q38">
+        <v>-0.3667554509830654</v>
+      </c>
+      <c r="R38">
+        <v>-0.9598627255104583</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39">
@@ -28782,6 +30039,51 @@
       <c r="D39">
         <v>-1.116325102</v>
       </c>
+      <c r="E39">
+        <v>1.819897332735977</v>
+      </c>
+      <c r="F39">
+        <v>1.313867321289626</v>
+      </c>
+      <c r="G39">
+        <v>1.320464922246394</v>
+      </c>
+      <c r="H39">
+        <v>0.7431748325395935</v>
+      </c>
+      <c r="I39">
+        <v>1.715468589054845</v>
+      </c>
+      <c r="J39">
+        <v>2.035022582603474</v>
+      </c>
+      <c r="K39">
+        <v>0.3467209255742884</v>
+      </c>
+      <c r="L39">
+        <v>1.624804515317556</v>
+      </c>
+      <c r="M39">
+        <v>1.446205275673949</v>
+      </c>
+      <c r="N39">
+        <v>1.958042519923964</v>
+      </c>
+      <c r="O39">
+        <v>2.0686935085884</v>
+      </c>
+      <c r="P39">
+        <v>1.795991290789356</v>
+      </c>
+      <c r="Q39">
+        <v>-1.09939345169849</v>
+      </c>
+      <c r="R39">
+        <v>-1.137765258330276</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40">
@@ -28796,6 +30098,51 @@
       <c r="D40">
         <v>-3.948192815</v>
       </c>
+      <c r="E40">
+        <v>-1.793286347236064</v>
+      </c>
+      <c r="F40">
+        <v>-0.1115228758761262</v>
+      </c>
+      <c r="G40">
+        <v>-0.3672885731296679</v>
+      </c>
+      <c r="H40">
+        <v>0.9091537949904852</v>
+      </c>
+      <c r="I40">
+        <v>1.291172896148346</v>
+      </c>
+      <c r="J40">
+        <v>1.773289867592659</v>
+      </c>
+      <c r="K40">
+        <v>-0.9641519940863118</v>
+      </c>
+      <c r="L40">
+        <v>-0.7660738694767444</v>
+      </c>
+      <c r="M40">
+        <v>-0.4322510045336612</v>
+      </c>
+      <c r="N40">
+        <v>0.7767395554815084</v>
+      </c>
+      <c r="O40">
+        <v>0.4370776879741128</v>
+      </c>
+      <c r="P40">
+        <v>0.09539272412106613</v>
+      </c>
+      <c r="Q40">
+        <v>0.6636103390664273</v>
+      </c>
+      <c r="R40">
+        <v>-1.247243740065548</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -28809,6 +30156,385 @@
       </c>
       <c r="D41">
         <v>-0.75106377</v>
+      </c>
+      <c r="E41">
+        <v>-0.51918608435479</v>
+      </c>
+      <c r="F41">
+        <v>-0.1191609947052676</v>
+      </c>
+      <c r="G41">
+        <v>-1.521016894730918</v>
+      </c>
+      <c r="H41">
+        <v>-0.3096600511131481</v>
+      </c>
+      <c r="I41">
+        <v>0.5348197044454545</v>
+      </c>
+      <c r="J41">
+        <v>1.097654254425204</v>
+      </c>
+      <c r="K41">
+        <v>-0.2373238188475099</v>
+      </c>
+      <c r="L41">
+        <v>0.4927806905267941</v>
+      </c>
+      <c r="M41">
+        <v>0.06982899550855909</v>
+      </c>
+      <c r="N41">
+        <v>0.1919700504162635</v>
+      </c>
+      <c r="O41">
+        <v>-0.1708506662500838</v>
+      </c>
+      <c r="P41">
+        <v>-0.2053722369447112</v>
+      </c>
+      <c r="Q41">
+        <v>-0.9670034286746886</v>
+      </c>
+      <c r="R41">
+        <v>-0.7573275343002042</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>1968</v>
+      </c>
+      <c r="I42">
+        <v>-0.4798004307657409</v>
+      </c>
+      <c r="J42">
+        <v>-0.7588219799538375</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1969</v>
+      </c>
+      <c r="I43">
+        <v>-0.3045478619565342</v>
+      </c>
+      <c r="J43">
+        <v>-0.9535998143804912</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>1970</v>
+      </c>
+      <c r="I44">
+        <v>-0.6735006383969688</v>
+      </c>
+      <c r="J44">
+        <v>-0.1379676327188795</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>1971</v>
+      </c>
+      <c r="I45">
+        <v>-2.333788132378925</v>
+      </c>
+      <c r="J45">
+        <v>-0.3266586598197003</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>1972</v>
+      </c>
+      <c r="I46">
+        <v>-1.927940078294447</v>
+      </c>
+      <c r="J46">
+        <v>-0.3266586598197003</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>1973</v>
+      </c>
+      <c r="I47">
+        <v>0.05518109507288943</v>
+      </c>
+      <c r="J47">
+        <v>0.4646262925385798</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>1974</v>
+      </c>
+      <c r="I48">
+        <v>-1.402182371866827</v>
+      </c>
+      <c r="J48">
+        <v>0.1663727335727666</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>1975</v>
+      </c>
+      <c r="I49">
+        <v>0.6086102597335414</v>
+      </c>
+      <c r="J49">
+        <v>-0.04666552283138569</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>1976</v>
+      </c>
+      <c r="I50">
+        <v>0.3872385938692807</v>
+      </c>
+      <c r="J50">
+        <v>0.2028935775277643</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>1977</v>
+      </c>
+      <c r="I51">
+        <v>0.5348197044454545</v>
+      </c>
+      <c r="J51">
+        <v>-0.07101275213471731</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>1978</v>
+      </c>
+      <c r="I52">
+        <v>-0.6273815413419145</v>
+      </c>
+      <c r="J52">
+        <v>-1.568367354289616</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>1979</v>
+      </c>
+      <c r="I53">
+        <v>-1.595882579498056</v>
+      </c>
+      <c r="J53">
+        <v>-0.9353393924029927</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>1980</v>
+      </c>
+      <c r="I54">
+        <v>-0.2861002231345126</v>
+      </c>
+      <c r="J54">
+        <v>-1.446631207772958</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>1981</v>
+      </c>
+      <c r="I55">
+        <v>0.2488813027041178</v>
+      </c>
+      <c r="J55">
+        <v>-0.6005649894821818</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>2020</v>
+      </c>
+      <c r="E56">
+        <v>0.334409439305223</v>
+      </c>
+      <c r="F56">
+        <v>1.092932948844063</v>
+      </c>
+      <c r="G56">
+        <v>0.6194383264160057</v>
+      </c>
+      <c r="H56">
+        <v>1.974592356606052</v>
+      </c>
+      <c r="I56">
+        <v>1.060577410873074</v>
+      </c>
+      <c r="J56">
+        <v>1.925460050738482</v>
+      </c>
+      <c r="K56">
+        <v>-0.6325396232249667</v>
+      </c>
+      <c r="L56">
+        <v>0.8970232682396404</v>
+      </c>
+      <c r="M56">
+        <v>0.3520636116018487</v>
+      </c>
+      <c r="N56">
+        <v>-0.2823271919254097</v>
+      </c>
+      <c r="O56">
+        <v>-0.2486712048186485</v>
+      </c>
+      <c r="P56">
+        <v>-0.05939018238873323</v>
+      </c>
+      <c r="Q56">
+        <v>-1.412876252822269</v>
+      </c>
+      <c r="R56">
+        <v>-0.9133343707729673</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>2023</v>
+      </c>
+      <c r="E57">
+        <v>-0.2606935627491785</v>
+      </c>
+      <c r="F57">
+        <v>-1.01682314001398</v>
+      </c>
+      <c r="G57">
+        <v>-0.7790909306201942</v>
+      </c>
+      <c r="H57">
+        <v>-0.4989682967864782</v>
+      </c>
+      <c r="I57">
+        <v>1.438754006724519</v>
+      </c>
+      <c r="J57">
+        <v>1.024612566515209</v>
+      </c>
+      <c r="K57">
+        <v>-0.6803933525994899</v>
+      </c>
+      <c r="L57">
+        <v>0.08648669364807046</v>
+      </c>
+      <c r="M57">
+        <v>0.3084141778798065</v>
+      </c>
+      <c r="N57">
+        <v>0.3098684866181071</v>
+      </c>
+      <c r="O57">
+        <v>-0.03891875677566329</v>
+      </c>
+      <c r="P57">
+        <v>-0.6773801876227766</v>
+      </c>
+      <c r="Q57">
+        <v>1.580156652308127</v>
+      </c>
+      <c r="R57">
+        <v>-1.206189309414821</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>2024</v>
+      </c>
+      <c r="G58">
+        <v>-0.2993351401424489</v>
+      </c>
+      <c r="H58">
+        <v>-1.854046510264495</v>
+      </c>
+      <c r="I58">
+        <v>1.245053799093291</v>
+      </c>
+      <c r="J58">
+        <v>1.40199462071685</v>
+      </c>
+      <c r="K58">
+        <v>0.8845084346834061</v>
+      </c>
+      <c r="N58">
+        <v>-0.24408739852786</v>
+      </c>
+      <c r="O58">
+        <v>0.1473617710473445</v>
+      </c>
+      <c r="P58">
+        <v>1.005298404680961</v>
+      </c>
+      <c r="Q58">
+        <v>1.50228016817648</v>
+      </c>
+      <c r="R58">
+        <v>-0.7573275343002042</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -29541,7 +31267,7 @@
         <v>0</v>
       </c>
       <c r="AI2">
-        <v>1.536047499361734</v>
+        <v>1.669827427664081</v>
       </c>
     </row>
     <row r="3">
@@ -29623,7 +31349,7 @@
         <v>0</v>
       </c>
       <c r="AI3">
-        <v>1.382751902280152</v>
+        <v>1.39348437833776</v>
       </c>
     </row>
   </sheetData>
